--- a/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
@@ -1,39 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="TDSheet" sheetId="1" r:id="rId5"/>
+    <sheet name="TDSheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
-    <t>- - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - л и н и я о т р е з а - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - -</t>
+    <t xml:space="preserve">- - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - л и н и я о т р е з а - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - - -</t>
   </si>
   <si>
-    <t>Приложение 1
+    <t xml:space="preserve">Приложение 1
 к приказу Министра финансов Республики Казахстан
 от 20 декабря 2012 года № 562</t>
   </si>
   <si>
-    <t>Форма КО-1</t>
+    <t xml:space="preserve">Форма КО-1</t>
   </si>
   <si>
-    <t>Организация (индивидуальный предприниматель)</t>
+    <t xml:space="preserve">Организация (индивидуальный предприниматель)</t>
   </si>
   <si>
-    <t>Индивидуальный предприниматель                гостиница "XANSHA "                                                                  Рыспаева Гаухар Сериковна</t>
+    <t xml:space="preserve">Индивидуальный предприниматель                гостиница "XANSHA "                                                                  Рыспаева Гаухар Сериковна</t>
   </si>
   <si>
     <t>КВИТАНЦИЯ</t>
   </si>
   <si>
-    <t>к приходному кассовому ордеру</t>
+    <t xml:space="preserve">к приходному кассовому ордеру</t>
   </si>
   <si>
     <t>№</t>
@@ -42,7 +47,7 @@
     <t>{enumeration}</t>
   </si>
   <si>
-    <t>Принято от: через</t>
+    <t xml:space="preserve">Принято от: через</t>
   </si>
   <si>
     <t>{customer.fullnameClient}</t>
@@ -61,10 +66,10 @@
     <t>Сумма</t>
   </si>
   <si>
-    <t xml:space="preserve"> {totalPrice} тенге  00 тиын</t>
+    <t xml:space="preserve"> {totalCost} тенге  00 тиын</t>
   </si>
   <si>
-    <t xml:space="preserve">  ({totalPriceWords}) тенге 00 тиын</t>
+    <t xml:space="preserve">  ({totalCostRu}) тенге 00 тиын</t>
   </si>
   <si>
     <t>прописью</t>
@@ -79,13 +84,13 @@
     <t>/</t>
   </si>
   <si>
-    <t>" XANSHA" Рыспаева Г.С.</t>
+    <t xml:space="preserve">" XANSHA" Рыспаева Г.С.</t>
   </si>
   <si>
     <t>подпись</t>
   </si>
   <si>
-    <t>расшифровка подписи</t>
+    <t xml:space="preserve">расшифровка подписи</t>
   </si>
   <si>
     <t>Кассир</t>
@@ -94,46 +99,46 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8">
     <font>
-      <sz val="8.0"/>
-      <color rgb="FF000000"/>
+      <sz val="8.000000"/>
+      <color indexed="64"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="6.0"/>
+      <sz val="6.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <i/>
-      <sz val="7.0"/>
+      <sz val="7.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font/>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="8.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <i/>
-      <sz val="6.0"/>
+      <sz val="6.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -143,124 +148,419 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="28">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" textRotation="90" vertical="center" wrapText="0"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" textRotation="90" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf fontId="5" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf fontId="7" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -317,7 +617,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -343,7 +643,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -420,7 +720,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -450,26 +750,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="16.83" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="16.829999999999998" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" hidden="1" min="1" max="1" width="4.67"/>
-    <col customWidth="1" min="2" max="2" width="2.67"/>
-    <col customWidth="1" min="3" max="3" width="8.67"/>
+    <col customWidth="1" hidden="1" min="1" max="1" width="4.6699999999999999"/>
+    <col customWidth="1" min="2" max="2" width="2.6699999999999999"/>
+    <col customWidth="1" min="3" max="3" width="8.6699999999999999"/>
     <col customWidth="1" min="4" max="4" width="1.5"/>
-    <col customWidth="1" min="5" max="5" width="7.0"/>
-    <col customWidth="1" min="6" max="6" width="8.33"/>
-    <col customWidth="1" min="7" max="7" width="1.83"/>
+    <col customWidth="1" min="5" max="5" width="7"/>
+    <col customWidth="1" min="6" max="6" width="8.3300000000000001"/>
+    <col customWidth="1" min="7" max="7" width="1.8300000000000001"/>
     <col customWidth="1" min="8" max="8" width="13.17"/>
-    <col customWidth="1" hidden="1" min="9" max="9" width="9.83"/>
-    <col customWidth="1" min="10" max="26" width="8.0"/>
+    <col customWidth="1" hidden="1" min="9" max="9" width="9.8300000000000001"/>
+    <col customWidth="1" min="10" max="26" width="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="9.75" customHeight="1">
@@ -535,7 +837,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" ht="51.0" customHeight="1">
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="1"/>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -564,7 +866,7 @@
       </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" ht="12.0" customHeight="1">
+    <row r="12" ht="12" customHeight="1">
       <c r="A12" s="1"/>
       <c r="C12" s="9" t="s">
         <v>6</v>
@@ -595,7 +897,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" ht="15.0" customHeight="1">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1"/>
       <c r="C15" s="12" t="s">
         <v>9</v>
@@ -669,7 +971,7 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" ht="18.0" customHeight="1">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="1"/>
       <c r="C24" s="19" t="s">
         <v>14</v>
@@ -11420,6 +11722,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B3:B36"/>
+    <mergeCell ref="C3:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="F15:H15"/>
@@ -11435,17 +11744,10 @@
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="D34:F34"/>
     <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B3:B36"/>
-    <mergeCell ref="C3:I5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
@@ -53,7 +53,7 @@
     <t>{customer.fullnameClient}</t>
   </si>
   <si>
-    <t xml:space="preserve">{organization.organization}, г.{organization.city}, {organization.index}, {organization.address}
+    <t xml:space="preserve">{customer.organization.organization}, г.{customer.organization.city}, {customer.organization.index}, {customer.organization.address}
 </t>
   </si>
   <si>
@@ -103,7 +103,6 @@
   <fonts count="8">
     <font>
       <sz val="8.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -164,7 +163,7 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -172,7 +171,7 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
@@ -53,7 +53,7 @@
     <t>{customer.fullnameClient}</t>
   </si>
   <si>
-    <t xml:space="preserve">{customer.organization.organization}, г.{customer.organization.city}, {customer.organization.index}, {customer.organization.address}
+    <t xml:space="preserve">{customer.organization.organization}, г.{customer.organization.city}, {customer.organization.index} {customer.organization.address}
 </t>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Cash Receipt Order.xlsx
@@ -66,10 +66,10 @@
     <t>Сумма</t>
   </si>
   <si>
-    <t xml:space="preserve"> {totalCost} тенге  00 тиын</t>
+    <t xml:space="preserve"> {totalCost} тенге {totalCostCents} тиын</t>
   </si>
   <si>
-    <t xml:space="preserve">  ({totalCostRu}) тенге 00 тиын</t>
+    <t xml:space="preserve">  ({totalCostRu}) тенге{totalCostCentsRu} тиын</t>
   </si>
   <si>
     <t>прописью</t>
